--- a/test_data/RegBriefings/RegBriefings Tax Treaty Brief/RegBriefings Tax Treaty Brief_Test_Cases.xlsx
+++ b/test_data/RegBriefings/RegBriefings Tax Treaty Brief/RegBriefings Tax Treaty Brief_Test_Cases.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Tax Treaty Brief correctly shows 18 real country-pair entries (18 with 'Full Story' links on this environment).</t>
+          <t>Tax Treaty Brief correctly shows 35 real country-pair entries (35 with 'Full Story' links on this environment).</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Search correctly filtered from 18 to 2 entries, keeping 'Albania and Germany' visible.</t>
+          <t>Search correctly filtered from 35 to 1 entries, keeping 'Armenia and Japan' visible.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Searching 'Albania' leaves only matching pair entries, still visible</t>
+          <t>[PASS] Searching 'Armenia' leaves only matching pair entries, still visible</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Clearing the search box correctly restored all 18 entries.</t>
+          <t>Clearing the search box correctly restored all 35 entries.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
